--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-29.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-29.xlsx
@@ -576,22 +576,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>10.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-50</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.97</v>
+        <v>0.955</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1.39</v>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-29.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-29.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_08B534ECD9657E0F6235547658AE763DBDED92D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9B815E2-C1CC-4458-973D-3E0FCB8ECCEF}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_08B534ECD9657E0F6235547658AE763DBDED92D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{943E2C52-F989-4D63-90E9-49F0D1BACD10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,6 +308,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -677,8 +681,8 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <f>IF(L2=1,0.965/(H2-1),-1)</f>
-        <v>0.10179324894514767</v>
+        <f>IF(L2=1,0.965/(E2-1),-1)</f>
+        <v>0.20230607966457023</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -719,8 +723,8 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M14" si="0">IF(L3=1,0.965/(H3-1),-1)</f>
-        <v>0.10651214128035319</v>
+        <f t="shared" ref="M3:M14" si="0">IF(L3=1,0.965/(E3-1),-1)</f>
+        <v>0.19416498993963782</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -762,7 +766,7 @@
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>0.1800373134328358</v>
+        <v>0.1227735368956743</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -846,7 +850,7 @@
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>0.1316507503410641</v>
+        <v>0.16083333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -888,7 +892,7 @@
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.10651214128035319</v>
+        <v>0.19416498993963782</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -930,7 +934,7 @@
       </c>
       <c r="M8">
         <f t="shared" si="0"/>
-        <v>0.11156069364161848</v>
+        <v>0.18629343629343631</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -972,7 +976,7 @@
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
-        <v>0.12664041994750658</v>
+        <v>0.16637931034482759</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1014,7 +1018,7 @@
       </c>
       <c r="M10">
         <f t="shared" si="0"/>
-        <v>0.10651214128035319</v>
+        <v>0.19416498993963782</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1056,7 +1060,7 @@
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
-        <v>0.3754863813229572</v>
+        <v>6.8928571428571422E-2</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1098,7 +1102,7 @@
       </c>
       <c r="M12">
         <f t="shared" si="0"/>
-        <v>0.3754863813229572</v>
+        <v>6.8928571428571422E-2</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1140,7 +1144,7 @@
       </c>
       <c r="M13">
         <f t="shared" si="0"/>
-        <v>0.10179324894514767</v>
+        <v>0.20230607966457023</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -1182,7 +1186,7 @@
       </c>
       <c r="M14">
         <f t="shared" si="0"/>
-        <v>8.9684014869888473E-2</v>
+        <v>0.22705882352941176</v>
       </c>
     </row>
   </sheetData>
